--- a/R/PPML_Ratio_results.xlsx
+++ b/R/PPML_Ratio_results.xlsx
@@ -64,13 +64,13 @@
     <t xml:space="preserve">Mining &amp; quarrying</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0354 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0026 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0034 ns</t>
+    <t xml:space="preserve">0.0341 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0042 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0041 ns</t>
   </si>
   <si>
     <t xml:space="preserve">C17T18</t>
@@ -79,1063 +79,1063 @@
     <t xml:space="preserve">Paper &amp; printing</t>
   </si>
   <si>
-    <t xml:space="preserve">-0.0063 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0021 ns</t>
+    <t xml:space="preserve">-0.0027 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.002 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-3e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coke &amp; refined petroleum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0247 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0241 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0157 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chemicals &amp; chemical products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0092 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0011 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0017 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Non-metallic mineral products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0078 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0028 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0087 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Basic metals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0038 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0046 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0022 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D35_E36T39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electricity, gas &amp; water</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0016 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-7e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0031 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A01T03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agriculture, forestry &amp; fishing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.03 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0811 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1287 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C10T12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Food, beverages &amp; tobacco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0117 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C13T15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Textiles &amp; apparel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0123 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0057 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0065 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wood &amp; wood products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0032 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.022 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0139 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pharmaceuticals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1489 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0069 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rubber &amp; plastics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0034 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0048 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricated metal products</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.013 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0175 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0221 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Computers &amp; electronics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.028 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0023 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Electrical equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1369 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0047 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.004 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machinery &amp; equipment</t>
   </si>
   <si>
     <t xml:space="preserve">-4e-04 ns</t>
   </si>
   <si>
-    <t xml:space="preserve">C19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coke &amp; refined petroleum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0559 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0311 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.017 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chemicals &amp; chemical products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0081 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0012 ns</t>
+    <t xml:space="preserve">9e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0014 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Motor vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.006 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0066 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.1656 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other transport equipment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0077 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0035 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C31T33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other manufacturing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0073 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0024 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.016 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F41T43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Construction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G45T47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wholesale &amp; retail trade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0107 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0045 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0063 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Land transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0138 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0242 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0295 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Water transport</t>
   </si>
   <si>
     <t xml:space="preserve">3e-04 ns</t>
   </si>
   <si>
-    <t xml:space="preserve">C23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-metallic mineral products</t>
+    <t xml:space="preserve">-0.0155 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Air transport</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0284 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0374 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Warehousing &amp; support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.01 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0196 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0304 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">H53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Postal &amp; courier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0095 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0093 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0106 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I55T56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accommodation &amp; food services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.045 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0435 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0688 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J58T60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Publishing, TV &amp; broadcasting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0118 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0058 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0027 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J61</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecommunications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0264 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J62T63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT &amp; information services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0013 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0063 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0073 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K64T66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financial &amp; insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0062 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0047 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-6e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real estate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.023 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0206 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0649 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">M69T75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Professional &amp; technical services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-5e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0029 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">N77T82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Admin &amp; support services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0111 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0023 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P85</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Education</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0287 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0754 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0497 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Q86T88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Health &amp; social work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0328 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0431 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0098 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R90T93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arts &amp; entertainment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0047 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0192 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0248 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">S94T96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other service activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0218 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0651 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0371 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0036 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.001 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0021 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0022 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0043 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0237 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0037 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0027 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0029 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0132 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0016 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0018 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0095 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0013 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-9e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0025 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0046 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0296 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0367 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0141 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0098 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.008 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0011 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0136 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0264 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0216 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1901 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0086 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0075 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0025 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0033 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0053 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0082 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0058 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0723 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0064 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0734 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0015 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-1e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.001 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0115 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0243 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.2268 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0074 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0214 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.011 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0102 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0105 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0068 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0082 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0098 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0202 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0204 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0039 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.002 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0093 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0103 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0135 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0108 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0111 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0184 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.022 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0122 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0109 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0092 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0278 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.003 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0066 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0101 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0118 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0127 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0036 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0199 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0214 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0037 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0049 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0335 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0137 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0325 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0481 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0549 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0052 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0588 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0468 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0092 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0668 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0281 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0015 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0115 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0117 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0326 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0293 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0314 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0051 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0043 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0054 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0205 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0092 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0048 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0063 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0234 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0852 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0093 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0078 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0059 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0059 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0125 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0086 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0035 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0087 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0154 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1519 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0166 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0161 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0084 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0131 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-2e-04 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0302 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0179 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0147 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0244 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0068 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0072 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0065 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0412 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.3298 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.005 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.006 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0079 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0231 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.024 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0085 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0019 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0057 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0014 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0046 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0151 .</t>
   </si>
   <si>
     <t xml:space="preserve">7e-04 ns</t>
   </si>
   <si>
-    <t xml:space="preserve">0.006 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Basic metals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0062 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0038 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0012 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D35_E36T39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electricity, gas &amp; water</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0015 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0027 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A01T03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Agriculture, forestry &amp; fishing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0261 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0919 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1162 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C10T12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Food, beverages &amp; tobacco</t>
+    <t xml:space="preserve">-0.0051 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0108 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0079 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0044 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0268 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.021 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0262 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.029 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0057 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0047 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.004 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0107 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0088 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0109 **</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0041 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0216 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0073 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0045 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0049 .</t>
   </si>
   <si>
     <t xml:space="preserve">0.0085 ns</t>
   </si>
   <si>
-    <t xml:space="preserve">0.0069 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0062 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C13T15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Textiles &amp; apparel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0066 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0074 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0059 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wood &amp; wood products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0015 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.018 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0031 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pharmaceuticals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2242 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0091 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0117 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rubber &amp; plastics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0043 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0058 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0071 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabricated metal products</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.011 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0093 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0136 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Computers &amp; electronics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0419 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0042 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.001 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electrical equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.1349 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-9e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0016 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machinery &amp; equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0069 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0026 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Motor vehicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0074 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0107 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other transport equipment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0021 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0025 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0019 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C31T33</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other manufacturing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0069 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.013 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F41T43</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Construction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0016 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0023 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0086 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">G45T47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wholesale &amp; retail trade</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0057 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0065 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H49</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Land transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0096 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0233 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0238 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Water transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0011 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0085 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H51</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Air transport</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.008 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0241 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0281 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Warehousing &amp; support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0067 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0185 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0192 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">H53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Postal &amp; courier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0103 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0104 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0097 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I55T56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Accommodation &amp; food services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0422 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0518 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0606 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J58T60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Publishing, TV &amp; broadcasting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0115 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.006 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.003 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J61</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telecommunications</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0283 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0038 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J62T63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT &amp; information services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-8e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0076 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.009 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K64T66</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Financial &amp; insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0057 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0092 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0133 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Real estate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0219 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0271 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0516 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">M69T75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Professional &amp; technical services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0031 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0017 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0027 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N77T82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Admin &amp; support services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.01 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-3e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P85</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Education</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0218 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0491 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0391 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Q86T88</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Health &amp; social work</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0309 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.029 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0112 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">R90T93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arts &amp; entertainment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0167 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0197 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S94T96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other service activities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0409 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0093 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0366 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0035 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0059 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0022 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0429 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0317 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0244 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.003 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0037 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0029 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0188 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0052 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0037 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0113 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0057 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-1e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0082 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.035 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0092 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0071 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0052 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0053 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0084 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0182 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0128 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.2698 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0103 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0047 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0051 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0054 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0059 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.001 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0032 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0767 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0126 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0072 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0808 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0035 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-5e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-7e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0123 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0192 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.025 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0018 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0197 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0063 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0086 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0137 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0038 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0046 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0067 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.008 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0034 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0117 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0126 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0048 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0034 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0109 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.012 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0165 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0116 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0101 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0083 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0269 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0102 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0106 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0036 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0066 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0059 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0174 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0114 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0125 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0049 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0074 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0121 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0202 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0175 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0065 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0017 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0028 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0156 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0215 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0478 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0332 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0092 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0114 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0341 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0253 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0191 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0346 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0278 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0018 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0071 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0079 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0086 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0211 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0394 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0287 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0054 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0054 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0284 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0217 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0053 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0064 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-2e-04 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0272 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0509 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0041 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0031 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0102 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0024 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0044 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0087 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0139 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0161 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0061 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0086 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0084 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0107 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0058 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.011 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0366 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0203 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0173 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.022 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0072 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0065 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.027 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.028 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0187 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0068 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0205 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0056 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0027 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0045 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0049 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0083 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0037 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0073 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0167 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0127 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0137 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0101 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0231 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0188 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0232 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0075 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0202 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0077 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0094 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0073 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0144 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0292 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0122 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0082 .</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0114 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0161 ***</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0624 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0406 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.0443 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0347 *</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0246 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0142 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0235 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0211 ns</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0354 **</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.0022 ns</t>
+    <t xml:space="preserve">0.018 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0175 ***</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0336 *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0516 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0361 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0479 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0684 .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.024 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0141 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0691 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0585 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.0224 ns</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.0862 **</t>
   </si>
 </sst>
 </file>
@@ -1576,10 +1576,10 @@
         <v>16</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.0193</v>
+        <v>0.0181</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>33</v>
@@ -1588,10 +1588,10 @@
         <v>17</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0046</v>
+        <v>0.0054</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>7</v>
@@ -1600,10 +1600,10 @@
         <v>18</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.0031</v>
+        <v>0.0035</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>11</v>
@@ -1620,10 +1620,10 @@
         <v>21</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.003</v>
+        <v>0.0016</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>33</v>
@@ -1632,10 +1632,10 @@
         <v>22</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>7</v>
@@ -1644,10 +1644,10 @@
         <v>23</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.0037</v>
+        <v>0.0031</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>11</v>
@@ -1664,10 +1664,10 @@
         <v>26</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0228</v>
+        <v>0.0265</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>33</v>
@@ -1676,10 +1676,10 @@
         <v>27</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.0171</v>
+        <v>0.015</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>7</v>
@@ -1688,10 +1688,10 @@
         <v>28</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.0156</v>
+        <v>0.0131</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>11</v>
@@ -1708,34 +1708,34 @@
         <v>31</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0058</v>
+        <v>0.0056</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="4" t="s">
         <v>32</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.003</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="4" t="s">
         <v>33</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.0041</v>
+        <v>0.0034</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>11</v>
@@ -1752,10 +1752,10 @@
         <v>36</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.0141</v>
+        <v>0.0135</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>33</v>
@@ -1764,10 +1764,10 @@
         <v>37</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.0043</v>
+        <v>0.0018</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>7</v>
@@ -1776,10 +1776,10 @@
         <v>38</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0063</v>
+        <v>0.0069</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>11</v>
@@ -1792,14 +1792,14 @@
       <c r="B7" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="4" t="s">
         <v>41</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0072</v>
+        <v>0.0036</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>33</v>
@@ -1808,10 +1808,10 @@
         <v>42</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0029</v>
+        <v>0.0022</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>7</v>
@@ -1820,10 +1820,10 @@
         <v>43</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.0029</v>
+        <v>0.0016</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>11</v>
@@ -1840,22 +1840,22 @@
         <v>46</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.0044</v>
+        <v>0.0061</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="4" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.0014</v>
+        <v>0.0017</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>7</v>
@@ -1864,10 +1864,10 @@
         <v>48</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.0041</v>
+        <v>0.0046</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>11</v>
@@ -1884,10 +1884,10 @@
         <v>51</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0302</v>
+        <v>0.0319</v>
       </c>
       <c r="E9" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F9" t="n">
         <v>33</v>
@@ -1896,10 +1896,10 @@
         <v>52</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0576</v>
+        <v>0.0446</v>
       </c>
       <c r="I9" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
@@ -1908,10 +1908,10 @@
         <v>53</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0463</v>
+        <v>0.0458</v>
       </c>
       <c r="M9" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N9" t="n">
         <v>11</v>
@@ -1928,10 +1928,10 @@
         <v>56</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0055</v>
+        <v>0.0051</v>
       </c>
       <c r="E10" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F10" t="n">
         <v>33</v>
@@ -1940,10 +1940,10 @@
         <v>57</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0014</v>
+        <v>0.0016</v>
       </c>
       <c r="I10" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
@@ -1955,7 +1955,7 @@
         <v>0.0013</v>
       </c>
       <c r="M10" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N10" t="n">
         <v>11</v>
@@ -1972,10 +1972,10 @@
         <v>61</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0085</v>
+        <v>0.0096</v>
       </c>
       <c r="E11" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F11" t="n">
         <v>33</v>
@@ -1984,10 +1984,10 @@
         <v>62</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0042</v>
+        <v>0.0028</v>
       </c>
       <c r="I11" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J11" t="n">
         <v>7</v>
@@ -1996,10 +1996,10 @@
         <v>63</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0038</v>
+        <v>0.0025</v>
       </c>
       <c r="M11" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
@@ -2012,14 +2012,14 @@
       <c r="B12" t="s">
         <v>65</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="6" t="s">
         <v>66</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0082</v>
+        <v>0.0116</v>
       </c>
       <c r="E12" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
@@ -2028,10 +2028,10 @@
         <v>67</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0059</v>
+        <v>0.0061</v>
       </c>
       <c r="I12" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
@@ -2040,10 +2040,10 @@
         <v>68</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0208</v>
+        <v>0.0253</v>
       </c>
       <c r="M12" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N12" t="n">
         <v>11</v>
@@ -2060,10 +2060,10 @@
         <v>71</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0412</v>
+        <v>0.0408</v>
       </c>
       <c r="E13" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F13" t="n">
         <v>33</v>
@@ -2072,22 +2072,22 @@
         <v>72</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0096</v>
+        <v>0.0094</v>
       </c>
       <c r="I13" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0094</v>
+        <v>0.0088</v>
       </c>
       <c r="M13" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N13" t="n">
         <v>11</v>
@@ -2095,43 +2095,43 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="B14" t="s">
+      <c r="C14" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="E14" t="n">
+        <v>231</v>
+      </c>
+      <c r="F14" t="n">
+        <v>33</v>
+      </c>
+      <c r="G14" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="D14" t="n">
-        <v>0.0065</v>
-      </c>
-      <c r="E14" t="n">
-        <v>264</v>
-      </c>
-      <c r="F14" t="n">
-        <v>33</v>
-      </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="I14" t="n">
+        <v>49</v>
+      </c>
+      <c r="J14" t="n">
+        <v>7</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="H14" t="n">
-        <v>0.0073</v>
-      </c>
-      <c r="I14" t="n">
-        <v>56</v>
-      </c>
-      <c r="J14" t="n">
-        <v>7</v>
-      </c>
-      <c r="K14" s="5" t="s">
-        <v>78</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.0048</v>
+        <v>0.0042</v>
       </c>
       <c r="M14" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
@@ -2139,43 +2139,43 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="D15" t="n">
+        <v>0.0134</v>
+      </c>
+      <c r="E15" t="n">
+        <v>231</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="E15" t="n">
-        <v>264</v>
-      </c>
-      <c r="F15" t="n">
-        <v>33</v>
-      </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="I15" t="n">
+        <v>49</v>
+      </c>
+      <c r="J15" t="n">
+        <v>7</v>
+      </c>
+      <c r="K15" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="H15" t="n">
-        <v>0.0034</v>
-      </c>
-      <c r="I15" t="n">
-        <v>56</v>
-      </c>
-      <c r="J15" t="n">
-        <v>7</v>
-      </c>
-      <c r="K15" s="5" t="s">
-        <v>83</v>
-      </c>
       <c r="L15" t="n">
-        <v>0.008</v>
+        <v>0.0107</v>
       </c>
       <c r="M15" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
@@ -2183,43 +2183,43 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
         <v>84</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="D16" t="n">
+        <v>0.0047</v>
+      </c>
+      <c r="E16" t="n">
+        <v>231</v>
+      </c>
+      <c r="F16" t="n">
+        <v>33</v>
+      </c>
+      <c r="G16" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.0035</v>
-      </c>
-      <c r="E16" t="n">
-        <v>264</v>
-      </c>
-      <c r="F16" t="n">
-        <v>33</v>
-      </c>
-      <c r="G16" s="5" t="s">
+      <c r="H16" t="n">
+        <v>0.0076</v>
+      </c>
+      <c r="I16" t="n">
+        <v>49</v>
+      </c>
+      <c r="J16" t="n">
+        <v>7</v>
+      </c>
+      <c r="K16" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="H16" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="I16" t="n">
-        <v>56</v>
-      </c>
-      <c r="J16" t="n">
-        <v>7</v>
-      </c>
-      <c r="K16" s="5" t="s">
-        <v>88</v>
-      </c>
       <c r="L16" t="n">
-        <v>0.0065</v>
+        <v>0.007</v>
       </c>
       <c r="M16" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N16" t="n">
         <v>11</v>
@@ -2227,43 +2227,43 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
         <v>89</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="D17" t="n">
+        <v>0.0509</v>
+      </c>
+      <c r="E17" t="n">
+        <v>231</v>
+      </c>
+      <c r="F17" t="n">
+        <v>33</v>
+      </c>
+      <c r="G17" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D17" t="n">
-        <v>0.0417</v>
-      </c>
-      <c r="E17" t="n">
-        <v>264</v>
-      </c>
-      <c r="F17" t="n">
-        <v>33</v>
-      </c>
-      <c r="G17" s="6" t="s">
+      <c r="H17" t="n">
+        <v>0.0067</v>
+      </c>
+      <c r="I17" t="n">
+        <v>49</v>
+      </c>
+      <c r="J17" t="n">
+        <v>7</v>
+      </c>
+      <c r="K17" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="H17" t="n">
-        <v>0.0066</v>
-      </c>
-      <c r="I17" t="n">
-        <v>56</v>
-      </c>
-      <c r="J17" t="n">
-        <v>7</v>
-      </c>
-      <c r="K17" s="6" t="s">
-        <v>93</v>
-      </c>
       <c r="L17" t="n">
-        <v>0.0055</v>
+        <v>0.0054</v>
       </c>
       <c r="M17" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N17" t="n">
         <v>11</v>
@@ -2271,43 +2271,43 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="D18" t="n">
+        <v>0.0024</v>
+      </c>
+      <c r="E18" t="n">
+        <v>231</v>
+      </c>
+      <c r="F18" t="n">
+        <v>33</v>
+      </c>
+      <c r="G18" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.0031</v>
-      </c>
-      <c r="E18" t="n">
-        <v>264</v>
-      </c>
-      <c r="F18" t="n">
-        <v>33</v>
-      </c>
-      <c r="G18" s="5" t="s">
+      <c r="H18" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="I18" t="n">
+        <v>49</v>
+      </c>
+      <c r="J18" t="n">
+        <v>7</v>
+      </c>
+      <c r="K18" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="H18" t="n">
-        <v>0.0067</v>
-      </c>
-      <c r="I18" t="n">
-        <v>56</v>
-      </c>
-      <c r="J18" t="n">
-        <v>7</v>
-      </c>
-      <c r="K18" s="5" t="s">
-        <v>48</v>
-      </c>
       <c r="L18" t="n">
-        <v>0.0051</v>
+        <v>0.0057</v>
       </c>
       <c r="M18" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N18" t="n">
         <v>11</v>
@@ -2321,37 +2321,37 @@
         <v>99</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>68</v>
+        <v>100</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0075</v>
+        <v>0.008</v>
       </c>
       <c r="E19" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F19" t="n">
         <v>33</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H19" t="n">
-        <v>0.008</v>
+        <v>0.007</v>
       </c>
       <c r="I19" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J19" t="n">
         <v>7</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0086</v>
+        <v>0.041</v>
       </c>
       <c r="M19" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N19" t="n">
         <v>11</v>
@@ -2359,43 +2359,43 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0055</v>
+        <v>0.0058</v>
       </c>
       <c r="E20" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F20" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0033</v>
+        <v>0.0036</v>
       </c>
       <c r="I20" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>106</v>
+        <v>37</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0042</v>
+        <v>0.005</v>
       </c>
       <c r="M20" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N20" t="n">
         <v>11</v>
@@ -2412,10 +2412,10 @@
         <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0113</v>
+        <v>0.0138</v>
       </c>
       <c r="E21" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
@@ -2424,10 +2424,10 @@
         <v>110</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0044</v>
+        <v>0.0038</v>
       </c>
       <c r="I21" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
@@ -2436,10 +2436,10 @@
         <v>111</v>
       </c>
       <c r="L21" t="n">
-        <v>0.016</v>
+        <v>0.0189</v>
       </c>
       <c r="M21" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N21" t="n">
         <v>11</v>
@@ -2453,37 +2453,37 @@
         <v>113</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>114</v>
+        <v>37</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0148</v>
+        <v>0.0173</v>
       </c>
       <c r="E22" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>115</v>
+      <c r="G22" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0085</v>
+        <v>0.0043</v>
       </c>
       <c r="I22" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0191</v>
+        <v>0.0215</v>
       </c>
       <c r="M22" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N22" t="n">
         <v>11</v>
@@ -2491,43 +2491,43 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0065</v>
+      </c>
+      <c r="E23" t="n">
+        <v>231</v>
+      </c>
+      <c r="F23" t="n">
+        <v>33</v>
+      </c>
+      <c r="G23" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="B23" t="s">
+      <c r="H23" t="n">
+        <v>0.0032</v>
+      </c>
+      <c r="I23" t="n">
+        <v>49</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.0062</v>
-      </c>
-      <c r="E23" t="n">
-        <v>264</v>
-      </c>
-      <c r="F23" t="n">
-        <v>33</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0.0027</v>
-      </c>
-      <c r="I23" t="n">
-        <v>56</v>
-      </c>
-      <c r="J23" t="n">
-        <v>7</v>
-      </c>
-      <c r="K23" s="5" t="s">
-        <v>120</v>
-      </c>
       <c r="L23" t="n">
-        <v>0.0035</v>
+        <v>0.0038</v>
       </c>
       <c r="M23" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N23" t="n">
         <v>11</v>
@@ -2535,43 +2535,43 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
+        <v>119</v>
+      </c>
+      <c r="B24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D24" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="E24" t="n">
+        <v>231</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33</v>
+      </c>
+      <c r="G24" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="H24" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="I24" t="n">
+        <v>49</v>
+      </c>
+      <c r="J24" t="n">
+        <v>7</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.0085</v>
-      </c>
-      <c r="E24" t="n">
-        <v>264</v>
-      </c>
-      <c r="F24" t="n">
-        <v>33</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0047</v>
-      </c>
-      <c r="I24" t="n">
-        <v>56</v>
-      </c>
-      <c r="J24" t="n">
-        <v>7</v>
-      </c>
-      <c r="K24" s="5" t="s">
-        <v>125</v>
-      </c>
       <c r="L24" t="n">
-        <v>0.0055</v>
+        <v>0.0057</v>
       </c>
       <c r="M24" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N24" t="n">
         <v>11</v>
@@ -2579,43 +2579,43 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
+        <v>124</v>
+      </c>
+      <c r="B25" t="s">
+        <v>125</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="E25" t="n">
+        <v>231</v>
+      </c>
+      <c r="F25" t="n">
+        <v>33</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="B25" t="s">
+      <c r="H25" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="I25" t="n">
+        <v>49</v>
+      </c>
+      <c r="J25" t="n">
+        <v>7</v>
+      </c>
+      <c r="K25" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C25" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.0023</v>
-      </c>
-      <c r="E25" t="n">
-        <v>264</v>
-      </c>
-      <c r="F25" t="n">
-        <v>33</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0.0016</v>
-      </c>
-      <c r="I25" t="n">
-        <v>56</v>
-      </c>
-      <c r="J25" t="n">
-        <v>7</v>
-      </c>
-      <c r="K25" s="6" t="s">
-        <v>129</v>
-      </c>
       <c r="L25" t="n">
-        <v>0.0056</v>
+        <v>0.0091</v>
       </c>
       <c r="M25" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N25" t="n">
         <v>11</v>
@@ -2623,43 +2623,43 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
+        <v>128</v>
+      </c>
+      <c r="B26" t="s">
+        <v>129</v>
+      </c>
+      <c r="C26" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0143</v>
+      </c>
+      <c r="E26" t="n">
+        <v>231</v>
+      </c>
+      <c r="F26" t="n">
+        <v>33</v>
+      </c>
+      <c r="G26" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="B26" t="s">
+      <c r="H26" t="n">
+        <v>0.0059</v>
+      </c>
+      <c r="I26" t="n">
+        <v>49</v>
+      </c>
+      <c r="J26" t="n">
+        <v>7</v>
+      </c>
+      <c r="K26" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="C26" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.0135</v>
-      </c>
-      <c r="E26" t="n">
-        <v>264</v>
-      </c>
-      <c r="F26" t="n">
-        <v>33</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0.0096</v>
-      </c>
-      <c r="I26" t="n">
-        <v>56</v>
-      </c>
-      <c r="J26" t="n">
-        <v>7</v>
-      </c>
-      <c r="K26" s="5" t="s">
-        <v>134</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.0123</v>
+        <v>0.0122</v>
       </c>
       <c r="M26" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
@@ -2667,43 +2667,43 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
+        <v>132</v>
+      </c>
+      <c r="B27" t="s">
+        <v>133</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="E27" t="n">
+        <v>231</v>
+      </c>
+      <c r="F27" t="n">
+        <v>33</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="B27" t="s">
+      <c r="H27" t="n">
+        <v>0.0058</v>
+      </c>
+      <c r="I27" t="n">
+        <v>49</v>
+      </c>
+      <c r="J27" t="n">
+        <v>7</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="C27" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.0093</v>
-      </c>
-      <c r="E27" t="n">
-        <v>264</v>
-      </c>
-      <c r="F27" t="n">
-        <v>33</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0.0061</v>
-      </c>
-      <c r="I27" t="n">
-        <v>56</v>
-      </c>
-      <c r="J27" t="n">
-        <v>7</v>
-      </c>
-      <c r="K27" s="5" t="s">
-        <v>139</v>
-      </c>
       <c r="L27" t="n">
-        <v>0.0055</v>
+        <v>0.008</v>
       </c>
       <c r="M27" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
@@ -2711,43 +2711,43 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28" t="s">
+        <v>138</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0043</v>
+      </c>
+      <c r="E28" t="n">
+        <v>231</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33</v>
+      </c>
+      <c r="G28" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="B28" t="s">
+      <c r="H28" t="n">
+        <v>0.0019</v>
+      </c>
+      <c r="I28" t="n">
+        <v>49</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="C28" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="E28" t="n">
-        <v>264</v>
-      </c>
-      <c r="F28" t="n">
-        <v>33</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.0018</v>
-      </c>
-      <c r="I28" t="n">
-        <v>56</v>
-      </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>144</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.002</v>
+        <v>0.0021</v>
       </c>
       <c r="M28" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N28" t="n">
         <v>11</v>
@@ -2755,43 +2755,43 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
+        <v>142</v>
+      </c>
+      <c r="B29" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="E29" t="n">
+        <v>231</v>
+      </c>
+      <c r="F29" t="n">
+        <v>33</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B29" t="s">
+      <c r="H29" t="n">
+        <v>0.0163</v>
+      </c>
+      <c r="I29" t="n">
+        <v>49</v>
+      </c>
+      <c r="J29" t="n">
+        <v>7</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="C29" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.018</v>
-      </c>
-      <c r="E29" t="n">
-        <v>264</v>
-      </c>
-      <c r="F29" t="n">
-        <v>33</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="I29" t="n">
-        <v>56</v>
-      </c>
-      <c r="J29" t="n">
-        <v>7</v>
-      </c>
-      <c r="K29" s="5" t="s">
-        <v>149</v>
       </c>
       <c r="L29" t="n">
         <v>0.0319</v>
       </c>
       <c r="M29" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N29" t="n">
         <v>11</v>
@@ -2799,43 +2799,43 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B30" t="s">
+        <v>148</v>
+      </c>
+      <c r="C30" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0054</v>
+      </c>
+      <c r="E30" t="n">
+        <v>231</v>
+      </c>
+      <c r="F30" t="n">
+        <v>33</v>
+      </c>
+      <c r="G30" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="B30" t="s">
+      <c r="H30" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="I30" t="n">
+        <v>49</v>
+      </c>
+      <c r="J30" t="n">
+        <v>7</v>
+      </c>
+      <c r="K30" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="C30" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.0055</v>
-      </c>
-      <c r="E30" t="n">
-        <v>264</v>
-      </c>
-      <c r="F30" t="n">
-        <v>33</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.0025</v>
-      </c>
-      <c r="I30" t="n">
-        <v>56</v>
-      </c>
-      <c r="J30" t="n">
-        <v>7</v>
-      </c>
-      <c r="K30" s="5" t="s">
-        <v>154</v>
-      </c>
       <c r="L30" t="n">
-        <v>0.0031</v>
+        <v>0.0035</v>
       </c>
       <c r="M30" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N30" t="n">
         <v>11</v>
@@ -2843,43 +2843,43 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D31" t="n">
-        <v>0.023</v>
+        <v>0.0193</v>
       </c>
       <c r="E31" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F31" t="n">
         <v>33</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0015</v>
+        <v>0.0017</v>
       </c>
       <c r="I31" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0055</v>
+        <v>0.0033</v>
       </c>
       <c r="M31" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N31" t="n">
         <v>11</v>
@@ -2887,43 +2887,43 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>161</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>162</v>
+        <v>156</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0049</v>
+        <v>0.0047</v>
       </c>
       <c r="E32" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F32" t="n">
         <v>33</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0017</v>
+        <v>0.0023</v>
       </c>
       <c r="I32" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J32" t="n">
         <v>7</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0027</v>
+        <v>0.0026</v>
       </c>
       <c r="M32" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N32" t="n">
         <v>11</v>
@@ -2931,43 +2931,43 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0044</v>
+        <v>0.0037</v>
       </c>
       <c r="E33" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F33" t="n">
         <v>33</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0048</v>
+        <v>0.0023</v>
       </c>
       <c r="I33" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J33" t="n">
         <v>7</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0096</v>
+        <v>0.0037</v>
       </c>
       <c r="M33" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N33" t="n">
         <v>11</v>
@@ -2975,43 +2975,43 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0258</v>
+        <v>0.0251</v>
       </c>
       <c r="E34" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F34" t="n">
         <v>33</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0217</v>
+        <v>0.0136</v>
       </c>
       <c r="I34" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J34" t="n">
         <v>7</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="L34" t="n">
-        <v>0.02</v>
+        <v>0.0209</v>
       </c>
       <c r="M34" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N34" t="n">
         <v>11</v>
@@ -3019,43 +3019,43 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>177</v>
+        <v>171</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>172</v>
       </c>
       <c r="D35" t="n">
-        <v>0.006</v>
+        <v>0.0048</v>
       </c>
       <c r="E35" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" s="6" t="s">
-        <v>178</v>
+        <v>46</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0056</v>
+        <v>0.0053</v>
       </c>
       <c r="I35" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J35" t="n">
         <v>7</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0036</v>
+        <v>0.0044</v>
       </c>
       <c r="M35" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N35" t="n">
         <v>11</v>
@@ -3063,43 +3063,43 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="D36" t="n">
-        <v>0.007</v>
+        <v>0.0073</v>
       </c>
       <c r="E36" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F36" t="n">
         <v>33</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="H36" t="n">
+        <v>0.0111</v>
+      </c>
+      <c r="I36" t="n">
+        <v>49</v>
+      </c>
+      <c r="J36" t="n">
+        <v>7</v>
+      </c>
+      <c r="K36" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="L36" t="n">
         <v>0.0102</v>
       </c>
-      <c r="I36" t="n">
-        <v>56</v>
-      </c>
-      <c r="J36" t="n">
-        <v>7</v>
-      </c>
-      <c r="K36" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0.0081</v>
-      </c>
       <c r="M36" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N36" t="n">
         <v>11</v>
@@ -3107,43 +3107,43 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="D37" t="n">
-        <v>0.016</v>
+        <v>0.0182</v>
       </c>
       <c r="E37" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F37" t="n">
         <v>33</v>
       </c>
       <c r="G37" s="5" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0358</v>
+        <v>0.0564</v>
       </c>
       <c r="I37" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J37" t="n">
         <v>7</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0321</v>
+        <v>0.0384</v>
       </c>
       <c r="M37" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N37" t="n">
         <v>11</v>
@@ -3151,43 +3151,43 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0207</v>
+        <v>0.0226</v>
       </c>
       <c r="E38" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F38" t="n">
         <v>33</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0317</v>
+        <v>0.0454</v>
       </c>
       <c r="I38" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0356</v>
+        <v>0.0447</v>
       </c>
       <c r="M38" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N38" t="n">
         <v>11</v>
@@ -3195,43 +3195,43 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
-      </c>
-      <c r="C39" s="6" t="s">
-        <v>179</v>
+        <v>189</v>
+      </c>
+      <c r="C39" s="5" t="s">
+        <v>190</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0168</v>
+        <v>0.0262</v>
       </c>
       <c r="E39" t="n">
-        <v>264</v>
+        <v>231</v>
       </c>
       <c r="F39" t="n">
         <v>33</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0247</v>
+        <v>0.0311</v>
       </c>
       <c r="I39" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J39" t="n">
         <v>7</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0253</v>
+        <v>0.0361</v>
       </c>
       <c r="M39" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N39" t="n">
         <v>11</v>
@@ -3239,43 +3239,43 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C40" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0303</v>
+      </c>
+      <c r="E40" t="n">
+        <v>231</v>
+      </c>
+      <c r="F40" t="n">
+        <v>33</v>
+      </c>
+      <c r="G40" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="D40" t="n">
-        <v>0.0235</v>
-      </c>
-      <c r="E40" t="n">
-        <v>264</v>
-      </c>
-      <c r="F40" t="n">
-        <v>33</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>200</v>
-      </c>
       <c r="H40" t="n">
-        <v>0.0451</v>
+        <v>0.0552</v>
       </c>
       <c r="I40" t="n">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="J40" t="n">
         <v>7</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>201</v>
+        <v>28</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0437</v>
+        <v>0.0518</v>
       </c>
       <c r="M40" t="n">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="N40" t="n">
         <v>11</v>
@@ -3360,37 +3360,37 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.0222</v>
+        <v>0.022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>68</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.003</v>
+        <v>0.0034</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>0.003</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>11</v>
@@ -3403,38 +3403,38 @@
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>204</v>
+      <c r="C3" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0034</v>
+        <v>0.0019</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>106</v>
+        <v>200</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.0021</v>
+        <v>0.0028</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.0025</v>
+        <v>0.0031</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>11</v>
@@ -3447,38 +3447,38 @@
       <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>206</v>
+      <c r="C4" s="3" t="s">
+        <v>202</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0199</v>
+        <v>0.0178</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.0189</v>
+        <v>0.0173</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.0205</v>
+        <v>0.0182</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>11</v>
@@ -3492,37 +3492,37 @@
         <v>30</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.0054</v>
+        <v>0.0052</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.0021</v>
+        <v>0.0012</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.0026</v>
+        <v>0.0018</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>11</v>
@@ -3536,37 +3536,37 @@
         <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.0112</v>
+        <v>0.011</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.0037</v>
+        <v>0.0043</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.0035</v>
+        <v>0.0041</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>11</v>
@@ -3580,37 +3580,37 @@
         <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0103</v>
+        <v>0.0064</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>33</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>36</v>
+      <c r="G7" s="4" t="s">
+        <v>211</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0018</v>
+        <v>0.0013</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K7" s="3" t="s">
-        <v>110</v>
+      <c r="K7" s="4" t="s">
+        <v>212</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.003</v>
+        <v>0.0023</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>11</v>
@@ -3624,37 +3624,37 @@
         <v>45</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.0055</v>
+        <v>0.0059</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>217</v>
+        <v>126</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.002</v>
+        <v>0.0018</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>218</v>
+      <c r="K8" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>11</v>
@@ -3667,38 +3667,38 @@
       <c r="B9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" s="6" t="s">
-        <v>162</v>
+      <c r="C9" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0288</v>
+        <v>0.0308</v>
       </c>
       <c r="E9" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F9" t="n">
         <v>33</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0226</v>
+        <v>0.0253</v>
       </c>
       <c r="I9" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0307</v>
+        <v>0.0343</v>
       </c>
       <c r="M9" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N9" t="n">
         <v>11</v>
@@ -3712,37 +3712,37 @@
         <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>72</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0059</v>
+        <v>0.0058</v>
       </c>
       <c r="E10" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F10" t="n">
         <v>33</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H10" t="n">
         <v>0.0013</v>
       </c>
       <c r="I10" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0016</v>
+        <v>0.0018</v>
       </c>
       <c r="M10" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N10" t="n">
         <v>11</v>
@@ -3755,38 +3755,38 @@
       <c r="B11" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>223</v>
+      <c r="C11" s="5" t="s">
+        <v>220</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0045</v>
+        <v>0.006</v>
       </c>
       <c r="E11" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F11" t="n">
         <v>33</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0031</v>
+        <v>0.0027</v>
       </c>
       <c r="I11" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J11" t="n">
         <v>7</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>154</v>
+        <v>206</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0031</v>
+        <v>0.003</v>
       </c>
       <c r="M11" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
@@ -3800,37 +3800,37 @@
         <v>65</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0087</v>
+        <v>0.0135</v>
       </c>
       <c r="E12" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0041</v>
+        <v>0.0044</v>
       </c>
       <c r="I12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0143</v>
+        <v>0.0235</v>
       </c>
       <c r="M12" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N12" t="n">
         <v>11</v>
@@ -3844,37 +3844,37 @@
         <v>70</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0611</v>
+        <v>0.0647</v>
       </c>
       <c r="E13" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F13" t="n">
         <v>33</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>56</v>
+        <v>226</v>
       </c>
       <c r="H13" t="n">
-        <v>0.006</v>
+        <v>0.0065</v>
       </c>
       <c r="I13" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="L13" t="n">
-        <v>0.006</v>
+        <v>0.0056</v>
       </c>
       <c r="M13" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N13" t="n">
         <v>11</v>
@@ -3882,43 +3882,43 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
       <c r="C14" s="5" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0048</v>
+        <v>0.004</v>
       </c>
       <c r="E14" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F14" t="n">
         <v>33</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>231</v>
+        <v>177</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0045</v>
+        <v>0.0042</v>
       </c>
       <c r="I14" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J14" t="n">
         <v>7</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="L14" t="n">
-        <v>0.004</v>
+        <v>0.0041</v>
       </c>
       <c r="M14" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
@@ -3926,43 +3926,43 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0062</v>
+        <v>0.0098</v>
       </c>
       <c r="E15" t="n">
+        <v>198</v>
+      </c>
+      <c r="F15" t="n">
+        <v>33</v>
+      </c>
+      <c r="G15" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="F15" t="n">
-        <v>33</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>234</v>
-      </c>
       <c r="H15" t="n">
-        <v>0.0042</v>
+        <v>0.0075</v>
       </c>
       <c r="I15" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J15" t="n">
         <v>7</v>
       </c>
-      <c r="K15" s="6" t="s">
-        <v>235</v>
+      <c r="K15" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="L15" t="n">
-        <v>0.005</v>
+        <v>0.0086</v>
       </c>
       <c r="M15" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
@@ -3970,43 +3970,43 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
         <v>84</v>
       </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
       <c r="C16" s="6" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0222</v>
+        <v>0.0117</v>
       </c>
       <c r="E16" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F16" t="n">
         <v>33</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0065</v>
+        <v>0.0071</v>
       </c>
       <c r="I16" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J16" t="n">
         <v>7</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>238</v>
+        <v>208</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0084</v>
+        <v>0.0088</v>
       </c>
       <c r="M16" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N16" t="n">
         <v>11</v>
@@ -4014,43 +4014,43 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
         <v>89</v>
       </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
       <c r="C17" s="5" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0231</v>
+        <v>0.0359</v>
       </c>
       <c r="E17" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F17" t="n">
         <v>33</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0022</v>
+        <v>0.003</v>
       </c>
       <c r="I17" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J17" t="n">
         <v>7</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>241</v>
+      <c r="K17" s="6" t="s">
+        <v>237</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0039</v>
+        <v>0.0038</v>
       </c>
       <c r="M17" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N17" t="n">
         <v>11</v>
@@ -4058,43 +4058,43 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" t="s">
-        <v>95</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>167</v>
+      <c r="C18" s="6" t="s">
+        <v>238</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0037</v>
+        <v>0.0036</v>
       </c>
       <c r="E18" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
       </c>
       <c r="G18" s="6" t="s">
-        <v>242</v>
+        <v>32</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0051</v>
+        <v>0.0048</v>
       </c>
       <c r="I18" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J18" t="n">
         <v>7</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0038</v>
+        <v>0.0039</v>
       </c>
       <c r="M18" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N18" t="n">
         <v>11</v>
@@ -4108,37 +4108,37 @@
         <v>99</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0094</v>
+        <v>0.0092</v>
       </c>
       <c r="E19" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F19" t="n">
         <v>33</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0082</v>
+        <v>0.0118</v>
       </c>
       <c r="I19" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J19" t="n">
         <v>7</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0144</v>
+        <v>0.0524</v>
       </c>
       <c r="M19" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N19" t="n">
         <v>11</v>
@@ -4146,43 +4146,43 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>114</v>
+        <v>243</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0059</v>
+        <v>0.0062</v>
       </c>
       <c r="E20" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F20" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>105</v>
+        <v>77</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0028</v>
+        <v>0.0037</v>
       </c>
       <c r="I20" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>247</v>
+        <v>202</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0046</v>
+        <v>0.0052</v>
       </c>
       <c r="M20" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N20" t="n">
         <v>11</v>
@@ -4196,37 +4196,37 @@
         <v>108</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0074</v>
+        <v>0.0093</v>
       </c>
       <c r="E21" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>249</v>
+        <v>204</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0052</v>
+        <v>0.0066</v>
       </c>
       <c r="I21" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0052</v>
+        <v>0.0064</v>
       </c>
       <c r="M21" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N21" t="n">
         <v>11</v>
@@ -4240,37 +4240,37 @@
         <v>113</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>251</v>
+        <v>68</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0143</v>
+        <v>0.0173</v>
       </c>
       <c r="E22" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
-      <c r="G22" s="5" t="s">
-        <v>252</v>
+      <c r="G22" s="6" t="s">
+        <v>198</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0074</v>
+        <v>0.0056</v>
       </c>
       <c r="I22" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0101</v>
+        <v>0.0128</v>
       </c>
       <c r="M22" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N22" t="n">
         <v>11</v>
@@ -4278,43 +4278,43 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0073</v>
+        <v>0.0079</v>
       </c>
       <c r="E23" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F23" t="n">
         <v>33</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="H23" t="n">
-        <v>0.001</v>
+        <v>0.0019</v>
       </c>
       <c r="I23" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J23" t="n">
         <v>7</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0033</v>
+        <v>0.0037</v>
       </c>
       <c r="M23" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N23" t="n">
         <v>11</v>
@@ -4322,43 +4322,43 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0035</v>
+        <v>0.006</v>
       </c>
       <c r="E24" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F24" t="n">
         <v>33</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0041</v>
+        <v>0.0064</v>
       </c>
       <c r="I24" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J24" t="n">
         <v>7</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0051</v>
+        <v>0.0077</v>
       </c>
       <c r="M24" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N24" t="n">
         <v>11</v>
@@ -4366,43 +4366,43 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0026</v>
+        <v>0.0056</v>
       </c>
       <c r="E25" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F25" t="n">
         <v>33</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0015</v>
+        <v>0.0009</v>
       </c>
       <c r="I25" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0028</v>
+        <v>0.0087</v>
       </c>
       <c r="M25" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N25" t="n">
         <v>11</v>
@@ -4410,43 +4410,43 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0071</v>
+        <v>0.0083</v>
       </c>
       <c r="E26" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F26" t="n">
         <v>33</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>230</v>
+        <v>257</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0062</v>
+        <v>0.0107</v>
       </c>
       <c r="I26" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>105</v>
+        <v>258</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0052</v>
+        <v>0.0091</v>
       </c>
       <c r="M26" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
@@ -4454,43 +4454,43 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>77</v>
+        <v>259</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0064</v>
+        <v>0.0093</v>
       </c>
       <c r="E27" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F27" t="n">
         <v>33</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0032</v>
+        <v>0.0059</v>
       </c>
       <c r="I27" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0064</v>
+        <v>0.0084</v>
       </c>
       <c r="M27" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
@@ -4498,43 +4498,43 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C28" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0037</v>
+      </c>
+      <c r="E28" t="n">
+        <v>198</v>
+      </c>
+      <c r="F28" t="n">
+        <v>33</v>
+      </c>
+      <c r="G28" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="I28" t="n">
+        <v>42</v>
+      </c>
+      <c r="J28" t="n">
+        <v>7</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>264</v>
       </c>
-      <c r="D28" t="n">
-        <v>0.0033</v>
-      </c>
-      <c r="E28" t="n">
-        <v>231</v>
-      </c>
-      <c r="F28" t="n">
-        <v>33</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.0008</v>
-      </c>
-      <c r="I28" t="n">
-        <v>49</v>
-      </c>
-      <c r="J28" t="n">
-        <v>7</v>
-      </c>
-      <c r="K28" s="5" t="s">
-        <v>266</v>
-      </c>
       <c r="L28" t="n">
-        <v>0.0018</v>
+        <v>0.0024</v>
       </c>
       <c r="M28" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N28" t="n">
         <v>11</v>
@@ -4542,43 +4542,43 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0117</v>
+        <v>0.0147</v>
       </c>
       <c r="E29" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F29" t="n">
         <v>33</v>
       </c>
       <c r="G29" s="5" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0139</v>
+        <v>0.0162</v>
       </c>
       <c r="I29" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J29" t="n">
         <v>7</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>269</v>
+        <v>226</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0093</v>
+        <v>0.0119</v>
       </c>
       <c r="M29" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N29" t="n">
         <v>11</v>
@@ -4586,43 +4586,43 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>270</v>
+        <v>148</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0038</v>
+        <v>0.0048</v>
       </c>
       <c r="E30" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F30" t="n">
         <v>33</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0012</v>
+        <v>0.0013</v>
       </c>
       <c r="I30" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J30" t="n">
         <v>7</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>272</v>
+        <v>58</v>
       </c>
       <c r="L30" t="n">
         <v>0.0009</v>
       </c>
       <c r="M30" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N30" t="n">
         <v>11</v>
@@ -4630,31 +4630,31 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>273</v>
+        <v>250</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0208</v>
+        <v>0.0205</v>
       </c>
       <c r="E31" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F31" t="n">
         <v>33</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>104</v>
+        <v>209</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0014</v>
+        <v>0.0015</v>
       </c>
       <c r="I31" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
@@ -4663,10 +4663,10 @@
         <v>268</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0078</v>
+        <v>0.0074</v>
       </c>
       <c r="M31" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N31" t="n">
         <v>11</v>
@@ -4674,43 +4674,43 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0052</v>
+        <v>0.0045</v>
       </c>
       <c r="E32" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F32" t="n">
         <v>33</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0006</v>
+        <v>0.0007</v>
       </c>
       <c r="I32" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J32" t="n">
         <v>7</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0022</v>
+        <v>0.0024</v>
       </c>
       <c r="M32" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N32" t="n">
         <v>11</v>
@@ -4718,43 +4718,43 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B33" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>277</v>
+        <v>249</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0046</v>
+        <v>0.0042</v>
       </c>
       <c r="E33" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F33" t="n">
         <v>33</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0029</v>
+        <v>0.0022</v>
       </c>
       <c r="I33" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J33" t="n">
         <v>7</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>279</v>
+        <v>32</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0069</v>
+        <v>0.0023</v>
       </c>
       <c r="M33" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N33" t="n">
         <v>11</v>
@@ -4762,43 +4762,43 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>154</v>
+        <v>266</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0366</v>
+        <v>0.0391</v>
       </c>
       <c r="E34" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F34" t="n">
         <v>33</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0186</v>
+        <v>0.0096</v>
       </c>
       <c r="I34" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J34" t="n">
         <v>7</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="L34" t="n">
-        <v>0.0165</v>
+        <v>0.0175</v>
       </c>
       <c r="M34" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N34" t="n">
         <v>11</v>
@@ -4806,43 +4806,43 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0053</v>
+        <v>0.005</v>
       </c>
       <c r="E35" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>283</v>
+        <v>97</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0044</v>
+        <v>0.0039</v>
       </c>
       <c r="I35" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J35" t="n">
         <v>7</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>283</v>
+        <v>126</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0036</v>
+        <v>0.0055</v>
       </c>
       <c r="M35" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N35" t="n">
         <v>11</v>
@@ -4850,43 +4850,43 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
-      </c>
-      <c r="C36" s="6" t="s">
-        <v>46</v>
+        <v>175</v>
+      </c>
+      <c r="C36" s="5" t="s">
+        <v>276</v>
       </c>
       <c r="D36" t="n">
-        <v>0.007</v>
+        <v>0.0087</v>
       </c>
       <c r="E36" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F36" t="n">
         <v>33</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0113</v>
+        <v>0.0108</v>
       </c>
       <c r="I36" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>231</v>
+        <v>277</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0094</v>
+        <v>0.0118</v>
       </c>
       <c r="M36" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N36" t="n">
         <v>11</v>
@@ -4894,43 +4894,43 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0147</v>
+        <v>0.0157</v>
       </c>
       <c r="E37" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F37" t="n">
         <v>33</v>
       </c>
-      <c r="G37" s="6" t="s">
-        <v>17</v>
+      <c r="G37" s="5" t="s">
+        <v>279</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0329</v>
+        <v>0.0577</v>
       </c>
       <c r="I37" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J37" t="n">
         <v>7</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>286</v>
+        <v>280</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0383</v>
+        <v>0.0466</v>
       </c>
       <c r="M37" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N37" t="n">
         <v>11</v>
@@ -4938,43 +4938,43 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0234</v>
+        <v>0.0275</v>
       </c>
       <c r="E38" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F38" t="n">
         <v>33</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>288</v>
+        <v>282</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0201</v>
+        <v>0.0361</v>
       </c>
       <c r="I38" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0343</v>
+        <v>0.0499</v>
       </c>
       <c r="M38" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N38" t="n">
         <v>11</v>
@@ -4982,43 +4982,43 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>290</v>
+        <v>66</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0168</v>
+        <v>0.03</v>
       </c>
       <c r="E39" t="n">
-        <v>231</v>
+        <v>198</v>
       </c>
       <c r="F39" t="n">
         <v>33</v>
       </c>
       <c r="G39" s="6" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0156</v>
+        <v>0.0247</v>
       </c>
       <c r="I39" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="J39" t="n">
         <v>7</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="L39" t="n">
-        <v>0.019</v>
+        <v>0.0343</v>
       </c>
       <c r="M39" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N39" t="n">
         <v>11</v>
@@ -5026,43 +5026,43 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
+        <v>193</v>
+      </c>
+      <c r="B40" t="s">
+        <v>194</v>
+      </c>
+      <c r="C40" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.0276</v>
+      </c>
+      <c r="E40" t="n">
         <v>198</v>
       </c>
-      <c r="B40" t="s">
+      <c r="F40" t="n">
+        <v>33</v>
+      </c>
+      <c r="G40" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.0438</v>
+      </c>
+      <c r="I40" t="n">
+        <v>42</v>
+      </c>
+      <c r="J40" t="n">
+        <v>7</v>
+      </c>
+      <c r="K40" s="5" t="s">
         <v>199</v>
       </c>
-      <c r="C40" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="D40" t="n">
-        <v>0.0208</v>
-      </c>
-      <c r="E40" t="n">
-        <v>231</v>
-      </c>
-      <c r="F40" t="n">
-        <v>33</v>
-      </c>
-      <c r="G40" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="H40" t="n">
-        <v>0.0302</v>
-      </c>
-      <c r="I40" t="n">
-        <v>49</v>
-      </c>
-      <c r="J40" t="n">
-        <v>7</v>
-      </c>
-      <c r="K40" s="5" t="s">
-        <v>167</v>
-      </c>
       <c r="L40" t="n">
-        <v>0.0394</v>
+        <v>0.0541</v>
       </c>
       <c r="M40" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="N40" t="n">
         <v>11</v>
@@ -5147,37 +5147,37 @@
         <v>15</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>0.027</v>
+        <v>0.0281</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>296</v>
+        <v>211</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.0031</v>
+        <v>0.0028</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K2" s="4" t="s">
-        <v>234</v>
+      <c r="K2" s="3" t="s">
+        <v>96</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>0.0027</v>
+        <v>0.0029</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N2" s="2" t="n">
         <v>11</v>
@@ -5190,38 +5190,38 @@
       <c r="B3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>297</v>
+      <c r="C3" s="3" t="s">
+        <v>289</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>0.0056</v>
+        <v>0.0035</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>0.0013</v>
+        <v>0.0006</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J3" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>0.0007</v>
+        <v>0.0012</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N3" s="2" t="n">
         <v>11</v>
@@ -5234,38 +5234,38 @@
       <c r="B4" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>300</v>
+      <c r="C4" s="3" t="s">
+        <v>292</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.0114</v>
+        <v>0.0146</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>0.0185</v>
+        <v>0.0174</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J4" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0.022</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N4" s="2" t="n">
         <v>11</v>
@@ -5279,37 +5279,37 @@
         <v>30</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>252</v>
+        <v>295</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>0.004</v>
+        <v>0.0033</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>0.0013</v>
+        <v>0.0015</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0.0019</v>
+        <v>0.0018</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>11</v>
@@ -5323,37 +5323,37 @@
         <v>35</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>0.014</v>
+        <v>0.0123</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>88</v>
+        <v>269</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>0.0034</v>
+        <v>0.0054</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>306</v>
+        <v>110</v>
       </c>
       <c r="L6" s="2" t="n">
-        <v>0.003</v>
+        <v>0.0039</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N6" s="2" t="n">
         <v>11</v>
@@ -5367,37 +5367,37 @@
         <v>40</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>0.0132</v>
+        <v>0.0056</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>0.0013</v>
+        <v>0.0012</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J7" s="2" t="n">
         <v>7</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>0.002</v>
+        <v>0.0017</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>11</v>
@@ -5411,37 +5411,37 @@
         <v>45</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>97</v>
+        <v>253</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>0.0052</v>
+        <v>0.0083</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>33</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>106</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>0.0026</v>
+        <v>0.0031</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="K8" s="4" t="s">
-        <v>310</v>
+      <c r="K8" s="3" t="s">
+        <v>199</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0.0018</v>
+        <v>0.0027</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>11</v>
@@ -5455,37 +5455,37 @@
         <v>50</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0296</v>
+        <v>0.034</v>
       </c>
       <c r="E9" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F9" t="n">
         <v>33</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0339</v>
+        <v>0.0309</v>
       </c>
       <c r="I9" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J9" t="n">
         <v>7</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>310</v>
+        <v>47</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0408</v>
+        <v>0.0486</v>
       </c>
       <c r="M9" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N9" t="n">
         <v>11</v>
@@ -5499,37 +5499,37 @@
         <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0072</v>
+        <v>0.0086</v>
       </c>
       <c r="E10" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F10" t="n">
         <v>33</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0014</v>
+        <v>0.0021</v>
       </c>
       <c r="I10" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J10" t="n">
         <v>7</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>104</v>
+        <v>306</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0021</v>
+        <v>0.0024</v>
       </c>
       <c r="M10" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N10" t="n">
         <v>11</v>
@@ -5543,37 +5543,37 @@
         <v>60</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0027</v>
+        <v>0.0041</v>
       </c>
       <c r="E11" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F11" t="n">
         <v>33</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>76</v>
+        <v>308</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0036</v>
+        <v>0.0024</v>
       </c>
       <c r="I11" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
         <v>7</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0017</v>
+        <v>0.0022</v>
       </c>
       <c r="M11" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N11" t="n">
         <v>11</v>
@@ -5587,37 +5587,37 @@
         <v>65</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>183</v>
+        <v>310</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0067</v>
+        <v>0.0133</v>
       </c>
       <c r="E12" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F12" t="n">
         <v>33</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0091</v>
+        <v>0.0156</v>
       </c>
       <c r="I12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J12" t="n">
         <v>7</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0134</v>
+        <v>0.0249</v>
       </c>
       <c r="M12" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N12" t="n">
         <v>11</v>
@@ -5631,37 +5631,37 @@
         <v>70</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0525</v>
+        <v>0.0545</v>
       </c>
       <c r="E13" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F13" t="n">
         <v>33</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="H13" t="n">
         <v>0.0087</v>
       </c>
       <c r="I13" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J13" t="n">
         <v>7</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01</v>
+        <v>0.0081</v>
       </c>
       <c r="M13" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N13" t="n">
         <v>11</v>
@@ -5669,43 +5669,43 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
+        <v>73</v>
+      </c>
+      <c r="B14" t="s">
         <v>74</v>
       </c>
-      <c r="B14" t="s">
-        <v>75</v>
-      </c>
       <c r="C14" s="5" t="s">
-        <v>322</v>
+        <v>201</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0039</v>
+        <v>0.0024</v>
       </c>
       <c r="E14" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F14" t="n">
         <v>33</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>323</v>
+        <v>159</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0032</v>
+        <v>0.0024</v>
       </c>
       <c r="I14" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J14" t="n">
         <v>7</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0026</v>
+        <v>0.0018</v>
       </c>
       <c r="M14" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N14" t="n">
         <v>11</v>
@@ -5713,43 +5713,43 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B15" t="s">
         <v>79</v>
       </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
       <c r="C15" s="6" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="D15" t="n">
-        <v>0.006</v>
+        <v>0.0088</v>
       </c>
       <c r="E15" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F15" t="n">
         <v>33</v>
       </c>
-      <c r="G15" s="6" t="s">
-        <v>326</v>
+      <c r="G15" s="5" t="s">
+        <v>275</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0069</v>
+        <v>0.008</v>
       </c>
       <c r="I15" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J15" t="n">
         <v>7</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0057</v>
+        <v>0.0082</v>
       </c>
       <c r="M15" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N15" t="n">
         <v>11</v>
@@ -5757,43 +5757,43 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B16" t="s">
         <v>84</v>
       </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
       <c r="C16" s="6" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0079</v>
+        <v>0.0046</v>
       </c>
       <c r="E16" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F16" t="n">
         <v>33</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0051</v>
+        <v>0.0047</v>
       </c>
       <c r="I16" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J16" t="n">
         <v>7</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0068</v>
+        <v>0.0058</v>
       </c>
       <c r="M16" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N16" t="n">
         <v>11</v>
@@ -5801,43 +5801,43 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B17" t="s">
         <v>89</v>
       </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>331</v>
+      <c r="C17" s="6" t="s">
+        <v>322</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0206</v>
+        <v>0.0123</v>
       </c>
       <c r="E17" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F17" t="n">
         <v>33</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0014</v>
+        <v>0.0022</v>
       </c>
       <c r="I17" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J17" t="n">
         <v>7</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>232</v>
+        <v>324</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0037</v>
+        <v>0.0035</v>
       </c>
       <c r="M17" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N17" t="n">
         <v>11</v>
@@ -5845,43 +5845,43 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
         <v>94</v>
       </c>
-      <c r="B18" t="s">
-        <v>95</v>
-      </c>
       <c r="C18" s="5" t="s">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="D18" t="n">
-        <v>0.004</v>
+        <v>0.0051</v>
       </c>
       <c r="E18" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F18" t="n">
         <v>33</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>167</v>
+        <v>325</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0067</v>
+        <v>0.0066</v>
       </c>
       <c r="I18" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J18" t="n">
         <v>7</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>87</v>
+        <v>326</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0052</v>
+        <v>0.0053</v>
       </c>
       <c r="M18" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N18" t="n">
         <v>11</v>
@@ -5895,37 +5895,37 @@
         <v>99</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>333</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0112</v>
+        <v>0.0088</v>
       </c>
       <c r="E19" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F19" t="n">
         <v>33</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="H19" t="n">
-        <v>0.006</v>
+        <v>0.0083</v>
       </c>
       <c r="I19" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J19" t="n">
         <v>7</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0174</v>
+        <v>0.0522</v>
       </c>
       <c r="M19" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N19" t="n">
         <v>11</v>
@@ -5933,43 +5933,43 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>179</v>
+        <v>104</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>329</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0071</v>
+        <v>0.0059</v>
       </c>
       <c r="E20" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F20" t="n">
         <v>33</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>154</v>
+        <v>330</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0022</v>
+        <v>0.0039</v>
       </c>
       <c r="I20" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J20" t="n">
         <v>7</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>76</v>
+        <v>331</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0038</v>
+        <v>0.0048</v>
       </c>
       <c r="M20" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N20" t="n">
         <v>11</v>
@@ -5983,37 +5983,37 @@
         <v>108</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0079</v>
+        <v>0.0097</v>
       </c>
       <c r="E21" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F21" t="n">
         <v>33</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>129</v>
+        <v>95</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0064</v>
+        <v>0.0067</v>
       </c>
       <c r="I21" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J21" t="n">
         <v>7</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>337</v>
+        <v>311</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0052</v>
+        <v>0.0072</v>
       </c>
       <c r="M21" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N21" t="n">
         <v>11</v>
@@ -6027,37 +6027,37 @@
         <v>113</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>338</v>
+        <v>333</v>
       </c>
       <c r="D22" t="n">
-        <v>0.01</v>
+        <v>0.0121</v>
       </c>
       <c r="E22" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F22" t="n">
         <v>33</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>339</v>
+        <v>214</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0036</v>
+        <v>0.0081</v>
       </c>
       <c r="I22" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J22" t="n">
         <v>7</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>282</v>
+        <v>75</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0111</v>
+        <v>0.0117</v>
       </c>
       <c r="M22" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N22" t="n">
         <v>11</v>
@@ -6065,43 +6065,43 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B23" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>18</v>
+        <v>334</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0081</v>
+        <v>0.0086</v>
       </c>
       <c r="E23" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F23" t="n">
         <v>33</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0012</v>
+        <v>0.0013</v>
       </c>
       <c r="I23" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J23" t="n">
         <v>7</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="L23" t="n">
-        <v>0.0036</v>
+        <v>0.0038</v>
       </c>
       <c r="M23" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N23" t="n">
         <v>11</v>
@@ -6109,43 +6109,43 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B24" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="6" t="s">
-        <v>342</v>
+        <v>120</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="D24" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="E24" t="n">
+        <v>165</v>
+      </c>
+      <c r="F24" t="n">
+        <v>33</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>336</v>
+      </c>
+      <c r="H24" t="n">
         <v>0.0068</v>
       </c>
-      <c r="E24" t="n">
-        <v>198</v>
-      </c>
-      <c r="F24" t="n">
-        <v>33</v>
-      </c>
-      <c r="G24" s="6" t="s">
-        <v>343</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.0109</v>
-      </c>
       <c r="I24" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J24" t="n">
         <v>7</v>
       </c>
-      <c r="K24" s="6" t="s">
-        <v>344</v>
+      <c r="K24" s="5" t="s">
+        <v>117</v>
       </c>
       <c r="L24" t="n">
-        <v>0.0039</v>
+        <v>0.0085</v>
       </c>
       <c r="M24" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N24" t="n">
         <v>11</v>
@@ -6153,43 +6153,43 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="B25" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>345</v>
+        <v>232</v>
       </c>
       <c r="D25" t="n">
-        <v>0.0035</v>
+        <v>0.0053</v>
       </c>
       <c r="E25" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F25" t="n">
         <v>33</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>66</v>
+      <c r="G25" s="6" t="s">
+        <v>337</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0028</v>
+        <v>0.002</v>
       </c>
       <c r="I25" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J25" t="n">
         <v>7</v>
       </c>
-      <c r="K25" s="5" t="s">
-        <v>137</v>
+      <c r="K25" s="6" t="s">
+        <v>338</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0045</v>
+        <v>0.0048</v>
       </c>
       <c r="M25" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N25" t="n">
         <v>11</v>
@@ -6197,43 +6197,43 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B26" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0049</v>
+        <v>0.0087</v>
       </c>
       <c r="E26" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F26" t="n">
         <v>33</v>
       </c>
-      <c r="G26" s="6" t="s">
-        <v>347</v>
+      <c r="G26" s="5" t="s">
+        <v>340</v>
       </c>
       <c r="H26" t="n">
         <v>0.0076</v>
       </c>
       <c r="I26" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J26" t="n">
         <v>7</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0035</v>
+        <v>0.0072</v>
       </c>
       <c r="M26" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N26" t="n">
         <v>11</v>
@@ -6241,43 +6241,43 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B27" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>17</v>
+        <v>133</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>208</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0047</v>
+        <v>0.0071</v>
       </c>
       <c r="E27" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F27" t="n">
         <v>33</v>
       </c>
-      <c r="G27" s="6" t="s">
-        <v>22</v>
+      <c r="G27" s="5" t="s">
+        <v>342</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0109</v>
+        <v>0.0043</v>
       </c>
       <c r="I27" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J27" t="n">
         <v>7</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>37</v>
+        <v>250</v>
       </c>
       <c r="L27" t="n">
-        <v>0.0052</v>
+        <v>0.0108</v>
       </c>
       <c r="M27" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N27" t="n">
         <v>11</v>
@@ -6285,43 +6285,43 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B28" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>349</v>
+        <v>231</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0061</v>
+        <v>0.0065</v>
       </c>
       <c r="E28" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F28" t="n">
         <v>33</v>
       </c>
       <c r="G28" s="5" t="s">
-        <v>97</v>
+        <v>343</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0017</v>
+        <v>0.0014</v>
       </c>
       <c r="I28" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J28" t="n">
         <v>7</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>241</v>
+        <v>344</v>
       </c>
       <c r="L28" t="n">
-        <v>0.0036</v>
+        <v>0.004</v>
       </c>
       <c r="M28" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N28" t="n">
         <v>11</v>
@@ -6329,43 +6329,43 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0109</v>
+        <v>0.0126</v>
       </c>
       <c r="E29" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F29" t="n">
         <v>33</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>351</v>
+        <v>346</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0085</v>
+        <v>0.0087</v>
       </c>
       <c r="I29" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J29" t="n">
         <v>7</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>352</v>
+        <v>347</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0092</v>
+        <v>0.0141</v>
       </c>
       <c r="M29" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N29" t="n">
         <v>11</v>
@@ -6373,43 +6373,43 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="B30" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>353</v>
+        <v>348</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0057</v>
+        <v>0.0143</v>
       </c>
       <c r="E30" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F30" t="n">
         <v>33</v>
       </c>
       <c r="G30" s="5" t="s">
-        <v>163</v>
+        <v>349</v>
       </c>
       <c r="H30" t="n">
-        <v>0.0016</v>
+        <v>0.0017</v>
       </c>
       <c r="I30" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J30" t="n">
         <v>7</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="L30" t="n">
-        <v>0.001</v>
+        <v>0.0009</v>
       </c>
       <c r="M30" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N30" t="n">
         <v>11</v>
@@ -6417,43 +6417,43 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B31" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0118</v>
+        <v>0.0065</v>
       </c>
       <c r="E31" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F31" t="n">
         <v>33</v>
       </c>
       <c r="G31" s="5" t="s">
-        <v>260</v>
+        <v>351</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0016</v>
+        <v>0.0014</v>
       </c>
       <c r="I31" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J31" t="n">
         <v>7</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>87</v>
+        <v>352</v>
       </c>
       <c r="L31" t="n">
-        <v>0.0058</v>
+        <v>0.0067</v>
       </c>
       <c r="M31" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N31" t="n">
         <v>11</v>
@@ -6461,43 +6461,43 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="B32" t="s">
-        <v>161</v>
-      </c>
-      <c r="C32" s="6" t="s">
-        <v>178</v>
+        <v>156</v>
+      </c>
+      <c r="C32" s="5" t="s">
+        <v>266</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0047</v>
+        <v>0.0033</v>
       </c>
       <c r="E32" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F32" t="n">
         <v>33</v>
       </c>
       <c r="G32" s="5" t="s">
-        <v>57</v>
+        <v>353</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0015</v>
+        <v>0.0018</v>
       </c>
       <c r="I32" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J32" t="n">
         <v>7</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>355</v>
+        <v>249</v>
       </c>
       <c r="L32" t="n">
-        <v>0.0039</v>
+        <v>0.004</v>
       </c>
       <c r="M32" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N32" t="n">
         <v>11</v>
@@ -6505,43 +6505,43 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
+        <v>160</v>
+      </c>
+      <c r="B33" t="s">
+        <v>161</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="E33" t="n">
         <v>165</v>
       </c>
-      <c r="B33" t="s">
-        <v>166</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>356</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.0048</v>
-      </c>
-      <c r="E33" t="n">
-        <v>198</v>
-      </c>
       <c r="F33" t="n">
         <v>33</v>
       </c>
       <c r="G33" s="5" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0038</v>
+        <v>0.0017</v>
       </c>
       <c r="I33" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J33" t="n">
         <v>7</v>
       </c>
-      <c r="K33" s="6" t="s">
-        <v>358</v>
+      <c r="K33" s="5" t="s">
+        <v>201</v>
       </c>
       <c r="L33" t="n">
-        <v>0.0097</v>
+        <v>0.0032</v>
       </c>
       <c r="M33" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N33" t="n">
         <v>11</v>
@@ -6549,43 +6549,43 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="B34" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>359</v>
+        <v>294</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0338</v>
+        <v>0.0345</v>
       </c>
       <c r="E34" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F34" t="n">
         <v>33</v>
       </c>
       <c r="G34" s="5" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="H34" t="n">
-        <v>0.0114</v>
+        <v>0.0096</v>
       </c>
       <c r="I34" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J34" t="n">
         <v>7</v>
       </c>
-      <c r="K34" s="6" t="s">
-        <v>234</v>
+      <c r="K34" s="5" t="s">
+        <v>214</v>
       </c>
       <c r="L34" t="n">
-        <v>0.012</v>
+        <v>0.0172</v>
       </c>
       <c r="M34" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N34" t="n">
         <v>11</v>
@@ -6593,43 +6593,43 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="B35" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0049</v>
+        <v>0.0055</v>
       </c>
       <c r="E35" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F35" t="n">
         <v>33</v>
       </c>
       <c r="G35" s="5" t="s">
-        <v>284</v>
+        <v>358</v>
       </c>
       <c r="H35" t="n">
-        <v>0.0032</v>
+        <v>0.0021</v>
       </c>
       <c r="I35" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J35" t="n">
         <v>7</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>153</v>
+        <v>359</v>
       </c>
       <c r="L35" t="n">
-        <v>0.0028</v>
+        <v>0.0027</v>
       </c>
       <c r="M35" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N35" t="n">
         <v>11</v>
@@ -6637,43 +6637,43 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="B36" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>41</v>
+        <v>360</v>
       </c>
       <c r="D36" t="n">
-        <v>0.0053</v>
+        <v>0.0068</v>
       </c>
       <c r="E36" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F36" t="n">
         <v>33</v>
       </c>
       <c r="G36" s="5" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H36" t="n">
         <v>0.0073</v>
       </c>
       <c r="I36" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J36" t="n">
         <v>7</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L36" t="n">
-        <v>0.0035</v>
+        <v>0.0046</v>
       </c>
       <c r="M36" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N36" t="n">
         <v>11</v>
@@ -6681,19 +6681,19 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="B37" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>182</v>
+        <v>363</v>
       </c>
       <c r="D37" t="n">
-        <v>0.0105</v>
+        <v>0.0132</v>
       </c>
       <c r="E37" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F37" t="n">
         <v>33</v>
@@ -6702,10 +6702,10 @@
         <v>364</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0458</v>
+        <v>0.0658</v>
       </c>
       <c r="I37" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J37" t="n">
         <v>7</v>
@@ -6714,10 +6714,10 @@
         <v>365</v>
       </c>
       <c r="L37" t="n">
-        <v>0.0371</v>
+        <v>0.0497</v>
       </c>
       <c r="M37" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N37" t="n">
         <v>11</v>
@@ -6725,19 +6725,19 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="B38" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="C38" s="5" t="s">
         <v>366</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0224</v>
+        <v>0.0307</v>
       </c>
       <c r="E38" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F38" t="n">
         <v>33</v>
@@ -6746,10 +6746,10 @@
         <v>367</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0164</v>
+        <v>0.0374</v>
       </c>
       <c r="I38" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J38" t="n">
         <v>7</v>
@@ -6758,10 +6758,10 @@
         <v>368</v>
       </c>
       <c r="L38" t="n">
-        <v>0.0259</v>
+        <v>0.0474</v>
       </c>
       <c r="M38" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N38" t="n">
         <v>11</v>
@@ -6769,19 +6769,19 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="B39" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="C39" s="6" t="s">
         <v>369</v>
       </c>
       <c r="D39" t="n">
-        <v>0.0174</v>
+        <v>0.0282</v>
       </c>
       <c r="E39" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F39" t="n">
         <v>33</v>
@@ -6790,10 +6790,10 @@
         <v>370</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0305</v>
+        <v>0.0439</v>
       </c>
       <c r="I39" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J39" t="n">
         <v>7</v>
@@ -6802,10 +6802,10 @@
         <v>371</v>
       </c>
       <c r="L39" t="n">
-        <v>0.0177</v>
+        <v>0.041</v>
       </c>
       <c r="M39" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N39" t="n">
         <v>11</v>
@@ -6813,43 +6813,43 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="B40" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>191</v>
+        <v>372</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0196</v>
+        <v>0.0296</v>
       </c>
       <c r="E40" t="n">
-        <v>198</v>
+        <v>165</v>
       </c>
       <c r="F40" t="n">
         <v>33</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0119</v>
+        <v>0.0315</v>
       </c>
       <c r="I40" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="J40" t="n">
         <v>7</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>373</v>
+        <v>187</v>
       </c>
       <c r="L40" t="n">
-        <v>0.0266</v>
+        <v>0.0494</v>
       </c>
       <c r="M40" t="n">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="N40" t="n">
         <v>11</v>
